--- a/artfynd/A 26870-2025 artfynd.xlsx
+++ b/artfynd/A 26870-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126381037</v>
+        <v>126382261</v>
       </c>
       <c r="B2" t="n">
         <v>78977</v>
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>335174</v>
+        <v>335074</v>
       </c>
       <c r="R2" t="n">
-        <v>6629074</v>
+        <v>6629249</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -800,41 +800,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126382261</v>
+        <v>126382808</v>
       </c>
       <c r="B3" t="n">
-        <v>78977</v>
+        <v>56848</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -842,10 +847,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>335074</v>
+        <v>335115</v>
       </c>
       <c r="R3" t="n">
-        <v>6629249</v>
+        <v>6629208</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,28 +891,12 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
           <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Levande träd # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -925,46 +914,41 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126382808</v>
+        <v>126381037</v>
       </c>
       <c r="B4" t="n">
-        <v>56848</v>
+        <v>78977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -972,10 +956,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>335115</v>
+        <v>335174</v>
       </c>
       <c r="R4" t="n">
-        <v>6629208</v>
+        <v>6629074</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1016,12 +1000,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
           <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Levande träd # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 26870-2025 artfynd.xlsx
+++ b/artfynd/A 26870-2025 artfynd.xlsx
@@ -800,46 +800,41 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126382808</v>
+        <v>126381037</v>
       </c>
       <c r="B3" t="n">
-        <v>56848</v>
+        <v>78977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -847,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>335115</v>
+        <v>335174</v>
       </c>
       <c r="R3" t="n">
-        <v>6629208</v>
+        <v>6629074</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -891,12 +886,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
           <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Levande träd # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -914,41 +925,46 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126381037</v>
+        <v>126382808</v>
       </c>
       <c r="B4" t="n">
-        <v>78977</v>
+        <v>56848</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -956,10 +972,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>335174</v>
+        <v>335115</v>
       </c>
       <c r="R4" t="n">
-        <v>6629074</v>
+        <v>6629208</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,28 +1016,12 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
           <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Levande träd # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -2289,38 +2289,41 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126382754</v>
+        <v>126381320</v>
       </c>
       <c r="B15" t="n">
-        <v>56848</v>
+        <v>78977</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2328,10 +2331,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>335045</v>
+        <v>335131</v>
       </c>
       <c r="R15" t="n">
-        <v>6629268</v>
+        <v>6629069</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2366,23 +2369,34 @@
           <t>2025-07-02</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Fjäder</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
           <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Levande träd # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2400,41 +2414,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126381320</v>
+        <v>126382754</v>
       </c>
       <c r="B16" t="n">
-        <v>78977</v>
+        <v>56848</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2442,10 +2453,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>335131</v>
+        <v>335045</v>
       </c>
       <c r="R16" t="n">
-        <v>6629069</v>
+        <v>6629268</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2480,34 +2491,23 @@
           <t>2025-07-02</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Fjäder</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
           <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Levande träd # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>

--- a/artfynd/A 26870-2025 artfynd.xlsx
+++ b/artfynd/A 26870-2025 artfynd.xlsx
@@ -2289,41 +2289,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126381320</v>
+        <v>126382754</v>
       </c>
       <c r="B15" t="n">
-        <v>78977</v>
+        <v>56848</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2331,10 +2328,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>335131</v>
+        <v>335045</v>
       </c>
       <c r="R15" t="n">
-        <v>6629069</v>
+        <v>6629268</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2369,34 +2366,23 @@
           <t>2025-07-02</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Fjäder</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
           <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Levande träd # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2414,38 +2400,41 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126382754</v>
+        <v>126381320</v>
       </c>
       <c r="B16" t="n">
-        <v>56848</v>
+        <v>78977</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2453,10 +2442,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>335045</v>
+        <v>335131</v>
       </c>
       <c r="R16" t="n">
-        <v>6629268</v>
+        <v>6629069</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2491,23 +2480,34 @@
           <t>2025-07-02</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Fjäder</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
           <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Levande träd # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>

--- a/artfynd/A 26870-2025 artfynd.xlsx
+++ b/artfynd/A 26870-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126382261</v>
       </c>
       <c r="B2" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>126381037</v>
       </c>
       <c r="B3" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>126382808</v>
       </c>
       <c r="B4" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>126382312</v>
       </c>
       <c r="B5" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>126382591</v>
       </c>
       <c r="B6" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>126382142</v>
       </c>
       <c r="B7" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>126381443</v>
       </c>
       <c r="B8" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         <v>126381372</v>
       </c>
       <c r="B9" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         <v>126381128</v>
       </c>
       <c r="B10" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>126382074</v>
       </c>
       <c r="B11" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>126382503</v>
       </c>
       <c r="B12" t="n">
-        <v>92724</v>
+        <v>92727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>126381941</v>
       </c>
       <c r="B13" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>126381264</v>
       </c>
       <c r="B14" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2289,38 +2289,41 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126382754</v>
+        <v>126381320</v>
       </c>
       <c r="B15" t="n">
-        <v>56848</v>
+        <v>78980</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2328,10 +2331,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>335045</v>
+        <v>335131</v>
       </c>
       <c r="R15" t="n">
-        <v>6629268</v>
+        <v>6629069</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2366,23 +2369,34 @@
           <t>2025-07-02</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Fjäder</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
           <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Levande träd # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2400,41 +2414,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126381320</v>
+        <v>126382754</v>
       </c>
       <c r="B16" t="n">
-        <v>78977</v>
+        <v>56849</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2442,10 +2453,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>335131</v>
+        <v>335045</v>
       </c>
       <c r="R16" t="n">
-        <v>6629069</v>
+        <v>6629268</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2480,34 +2491,23 @@
           <t>2025-07-02</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Fjäder</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
           <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Levande träd # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2528,7 +2528,7 @@
         <v>126381877</v>
       </c>
       <c r="B17" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
         <v>126382198</v>
       </c>
       <c r="B18" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 26870-2025 artfynd.xlsx
+++ b/artfynd/A 26870-2025 artfynd.xlsx
@@ -1289,7 +1289,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126382142</v>
+        <v>126381443</v>
       </c>
       <c r="B7" t="n">
         <v>78980</v>
@@ -1331,10 +1331,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>335124</v>
+        <v>335073</v>
       </c>
       <c r="R7" t="n">
-        <v>6629286</v>
+        <v>6629134</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1414,7 +1414,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126381443</v>
+        <v>126382142</v>
       </c>
       <c r="B8" t="n">
         <v>78980</v>
@@ -1456,10 +1456,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>335073</v>
+        <v>335124</v>
       </c>
       <c r="R8" t="n">
-        <v>6629134</v>
+        <v>6629286</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -2289,41 +2289,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126381320</v>
+        <v>126382754</v>
       </c>
       <c r="B15" t="n">
-        <v>78980</v>
+        <v>56849</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2331,10 +2328,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>335131</v>
+        <v>335045</v>
       </c>
       <c r="R15" t="n">
-        <v>6629069</v>
+        <v>6629268</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2369,34 +2366,23 @@
           <t>2025-07-02</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Fjäder</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
           <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Levande träd # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2414,38 +2400,41 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126382754</v>
+        <v>126381320</v>
       </c>
       <c r="B16" t="n">
-        <v>56849</v>
+        <v>78980</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2453,10 +2442,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>335045</v>
+        <v>335131</v>
       </c>
       <c r="R16" t="n">
-        <v>6629268</v>
+        <v>6629069</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2491,23 +2480,34 @@
           <t>2025-07-02</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Fjäder</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
           <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Levande träd # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>

--- a/artfynd/A 26870-2025 artfynd.xlsx
+++ b/artfynd/A 26870-2025 artfynd.xlsx
@@ -1039,10 +1039,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126382312</v>
+        <v>126382591</v>
       </c>
       <c r="B5" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1050,30 +1050,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1081,10 +1082,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>335053</v>
+        <v>335175</v>
       </c>
       <c r="R5" t="n">
-        <v>6629259</v>
+        <v>6629186</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1125,7 +1126,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1164,10 +1164,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126382591</v>
+        <v>126382312</v>
       </c>
       <c r="B6" t="n">
-        <v>57657</v>
+        <v>78980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1175,31 +1175,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1207,10 +1206,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>335175</v>
+        <v>335053</v>
       </c>
       <c r="R6" t="n">
-        <v>6629186</v>
+        <v>6629259</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1251,6 +1250,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -2289,38 +2289,41 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126382754</v>
+        <v>126381320</v>
       </c>
       <c r="B15" t="n">
-        <v>56849</v>
+        <v>78980</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2328,10 +2331,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>335045</v>
+        <v>335131</v>
       </c>
       <c r="R15" t="n">
-        <v>6629268</v>
+        <v>6629069</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2366,23 +2369,34 @@
           <t>2025-07-02</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Fjäder</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
           <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Levande träd # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2400,41 +2414,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126381320</v>
+        <v>126382754</v>
       </c>
       <c r="B16" t="n">
-        <v>78980</v>
+        <v>56849</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2442,10 +2453,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>335131</v>
+        <v>335045</v>
       </c>
       <c r="R16" t="n">
-        <v>6629069</v>
+        <v>6629268</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2480,34 +2491,23 @@
           <t>2025-07-02</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Fjäder</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
           <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Levande träd # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>

--- a/artfynd/A 26870-2025 artfynd.xlsx
+++ b/artfynd/A 26870-2025 artfynd.xlsx
@@ -2289,41 +2289,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126381320</v>
+        <v>126382754</v>
       </c>
       <c r="B15" t="n">
-        <v>78980</v>
+        <v>56849</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2331,10 +2328,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>335131</v>
+        <v>335045</v>
       </c>
       <c r="R15" t="n">
-        <v>6629069</v>
+        <v>6629268</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2369,34 +2366,23 @@
           <t>2025-07-02</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Fjäder</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
           <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Levande träd # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2414,38 +2400,41 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126382754</v>
+        <v>126381320</v>
       </c>
       <c r="B16" t="n">
-        <v>56849</v>
+        <v>78980</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2453,10 +2442,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>335045</v>
+        <v>335131</v>
       </c>
       <c r="R16" t="n">
-        <v>6629268</v>
+        <v>6629069</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2491,23 +2480,34 @@
           <t>2025-07-02</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Fjäder</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
           <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Levande träd # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>

--- a/artfynd/A 26870-2025 artfynd.xlsx
+++ b/artfynd/A 26870-2025 artfynd.xlsx
@@ -1039,10 +1039,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126382591</v>
+        <v>126382312</v>
       </c>
       <c r="B5" t="n">
-        <v>57657</v>
+        <v>78980</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1050,31 +1050,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1082,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>335175</v>
+        <v>335053</v>
       </c>
       <c r="R5" t="n">
-        <v>6629186</v>
+        <v>6629259</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,6 +1125,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1164,10 +1164,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126382312</v>
+        <v>126382591</v>
       </c>
       <c r="B6" t="n">
-        <v>78980</v>
+        <v>57657</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1175,30 +1175,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1206,10 +1207,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>335053</v>
+        <v>335175</v>
       </c>
       <c r="R6" t="n">
-        <v>6629259</v>
+        <v>6629186</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1250,7 +1251,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
